--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/3. RACI Matrix_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/3. RACI Matrix_VNS.xlsx
@@ -104,17 +104,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -134,12 +134,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -251,13 +251,13 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -650,7 +650,6 @@
     <col width="6.6" customWidth="1" min="11" max="11"/>
     <col width="6.6" customWidth="1" min="12" max="12"/>
     <col width="6.6" customWidth="1" min="13" max="13"/>
-    <col width="6.6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
@@ -710,22 +709,22 @@
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Project Sponsors &amp; University Leadership</t>
+          <t>Project Leadership</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Customer &amp; Users</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>University Technical Department</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
           <t>Project Team Members</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Project Sub-Teams</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>External Resources</t>
         </is>
       </c>
     </row>
@@ -737,62 +736,57 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lviv Polytechnic National University (Sponsor)</t>
+          <t>Lviv Polytechnic National University (Project Sponsor)</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Ministry of Education and Science (Sponsor)</t>
+          <t>Nataliia Shakhovska (Executive Sponsor, Rector)</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Nataliia Shakhovska (Rector)</t>
+          <t>Product Owner (K. Holovskyi)</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
+          <t>Project Manager (N. Zankovych)</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Business Analyst (A. Lysun)</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Tech Lead (D. Lunhul)</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>DevOps (Y. Shevchuk)</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>QA Specialist (V. Kamelchuk)</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
           <t>Nataliia Boiko (Customer / End user)</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>Technical Department of Lviv Polytechnic</t>
+        </is>
+      </c>
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>End users — students</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>Technical Department of Lviv Polytechnic</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>Product Owner (K. Holovskyi)</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>Project Manager (N. Zankovych)</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>Business Analyst (A. Lysun)</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>Tech Lead (D. Lunhul)</t>
-        </is>
-      </c>
-      <c r="M7" s="11" t="inlineStr">
-        <is>
-          <t>DevOps (Y. Shevchuk)</t>
-        </is>
-      </c>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>QA Specialist (V. Kamelchuk)</t>
         </is>
       </c>
     </row>
@@ -819,54 +813,49 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="K9" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L9" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M9" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -876,7 +865,7 @@
           <t xml:space="preserve"> - Identify and analyse stakeholders (register, power/interest matrix)</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -886,19 +875,19 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -906,19 +895,19 @@
           <t>I</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="K10" s="16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
@@ -927,11 +916,6 @@
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -953,52 +937,47 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="I11" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K11" s="15" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M11" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1010,62 +989,57 @@
           <t xml:space="preserve"> - Develop the business case and the success metrics</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1077,62 +1051,57 @@
           <t xml:space="preserve"> - Approve the project charter and the MVP scope</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K13" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L13" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M13" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1157,48 +1126,47 @@
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N15" s="15" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1216,50 +1184,49 @@
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="N16" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
     </row>
@@ -1275,48 +1242,47 @@
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N17" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
@@ -1329,57 +1295,52 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L18" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M18" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N18" s="14" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1391,7 +1352,7 @@
           <t xml:space="preserve"> - Produce the communications plan and the project schedule</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1401,54 +1362,49 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="K19" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L19" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M19" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N19" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L19" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1458,58 +1414,57 @@
           <t xml:space="preserve"> - Select the technology stack and the LLM API provider</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n"/>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L20" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N20" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
@@ -1524,56 +1479,55 @@
           <t xml:space="preserve"> - Obtain the student registry; implement registration and authentication</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K22" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="M22" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N22" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L22" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -1589,50 +1543,49 @@
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J23" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K23" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L23" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="M23" s="14" t="inlineStr">
         <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="N23" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
     </row>
@@ -1648,48 +1601,47 @@
         </is>
       </c>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>R/A</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K24" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>R/A</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M24" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N24" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1707,48 +1659,47 @@
         </is>
       </c>
       <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K25" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N25" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1766,44 +1717,43 @@
         </is>
       </c>
       <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K26" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M26" s="13" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="N26" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
@@ -1817,50 +1767,49 @@
         </is>
       </c>
       <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K27" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L27" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M27" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N27" s="13" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>R/A</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1826,7 @@
           <t xml:space="preserve"> - Manage scope changes and backlog priorities</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1887,52 +1836,47 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="K29" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L29" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L29" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N29" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
@@ -1950,50 +1894,49 @@
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L30" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M30" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N30" s="13" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>R/A</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2003,7 +1946,7 @@
           <t xml:space="preserve"> - Monitor LLM API costs, quotas and request limits</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2013,44 +1956,39 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="n"/>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n"/>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="K31" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L31" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M31" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="n"/>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
@@ -2068,54 +2006,49 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="K32" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L32" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="N32" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2065,7 @@
           <t xml:space="preserve"> - Run the pilot with students and collect feedback</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2142,54 +2075,49 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H34" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K34" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L34" s="15" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N34" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
     </row>
@@ -2199,64 +2127,59 @@
           <t xml:space="preserve"> - Hand over the system and documentation to the Technical Department and the customer</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L35" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M35" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N35" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M35" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2189,7 @@
           <t xml:space="preserve"> - Capture lessons learned and close the project</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2276,54 +2199,49 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="K36" s="16" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L36" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M36" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N36" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M36" s="14" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -2396,26 +2314,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C41:N41"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="C40:N40"/>
-    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B8:M8"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="C42:M42"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C43:N43"/>
-    <mergeCell ref="C39:N39"/>
+    <mergeCell ref="B38:M38"/>
+    <mergeCell ref="B28:M28"/>
+    <mergeCell ref="C41:M41"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="H6"/>
-    <mergeCell ref="B21:N21"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="I6:N6"/>
+    <mergeCell ref="C40:M40"/>
+    <mergeCell ref="B33:M33"/>
+    <mergeCell ref="C43:M43"/>
+    <mergeCell ref="K6:M6"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B14:N14"/>
-    <mergeCell ref="C42:N42"/>
-    <mergeCell ref="B8:N8"/>
+    <mergeCell ref="C39:M39"/>
+    <mergeCell ref="F6:H6"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="B38:N38"/>
-    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B21:M21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/3. RACI Matrix_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/3. RACI Matrix_VNS.xlsx
@@ -638,7 +638,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
     <col width="6.6" customWidth="1" min="3" max="3"/>
     <col width="6.6" customWidth="1" min="4" max="4"/>
     <col width="6.6" customWidth="1" min="5" max="5"/>
